--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486831_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486831_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2974</v>
+        <v>8.489000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2424</v>
+        <v>4.9802</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0551</v>
+        <v>3.5088</v>
       </c>
       <c r="G2" t="n">
         <v>12.5233</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0047</v>
+        <v>0.1868</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9381</v>
+        <v>-0.2003</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9333</v>
+        <v>0.387</v>
       </c>
       <c r="V2" t="n">
         <v>1.1851</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7989</v>
+        <v>3.9296</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7808</v>
+        <v>1.0172</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0181</v>
+        <v>2.9124</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4042</v>
+        <v>3.2631</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8829</v>
+        <v>2.6687</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5213</v>
+        <v>0.5945</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2126</v>
+        <v>3.2793</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0906</v>
+        <v>3.1526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1221</v>
+        <v>0.1267</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1916</v>
+        <v>-0.0161</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2077</v>
+        <v>-0.484</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3993</v>
+        <v>0.4678</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9308</v>
+        <v>3.0892</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6224</v>
+        <v>0.1452</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7952</v>
+        <v>0.1249</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3282</v>
+        <v>0.6138</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8995</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7957</v>
+        <v>3.7906</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1067</v>
+        <v>1.3188</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6889</v>
+        <v>2.4718</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2631</v>
+        <v>4.4042</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6687</v>
+        <v>2.8829</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5945</v>
+        <v>1.5213</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2793</v>
+        <v>3.2126</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1526</v>
+        <v>3.0906</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1267</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0161</v>
+        <v>1.1916</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.484</v>
+        <v>-0.2077</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4678</v>
+        <v>1.3993</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0892</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0112</v>
+        <v>0.6141</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1098</v>
+        <v>0.3652</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.2489</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3282</v>
+        <v>-1.2277</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>-0.3282</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9519</v>
+        <v>2.6609</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5965</v>
+        <v>0.8586</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3553</v>
+        <v>1.8023</v>
       </c>
       <c r="G5" t="n">
         <v>3.6491</v>
@@ -844,13 +844,13 @@
         <v>2.7031</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7778</v>
+        <v>-0.0688</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4142</v>
+        <v>-0.1521</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3636</v>
+        <v>0.0834</v>
       </c>
       <c r="V5" t="n">
         <v>2.1698</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3065</v>
+        <v>1.8279</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2563</v>
+        <v>1.6287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0502</v>
+        <v>0.1992</v>
       </c>
       <c r="G6" t="n">
         <v>1.8556</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.673</v>
+        <v>-0.1516</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6622</v>
+        <v>-0.2898</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0108</v>
+        <v>0.1382</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2277</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4896</v>
+        <v>-0.0412</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1986</v>
+        <v>-3.2468</v>
       </c>
       <c r="F7" t="n">
-        <v>2.709</v>
+        <v>3.2057</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6605</v>
@@ -1000,13 +1000,13 @@
         <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5242</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1934</v>
+        <v>-0.2417</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3307</v>
+        <v>0.1659</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6565</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7006</v>
+        <v>-0.3655</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5236</v>
+        <v>-1.2133</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8229</v>
+        <v>0.8478</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4139</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4798</v>
+        <v>-0.1447</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2759</v>
+        <v>0.0344</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2039</v>
+        <v>-0.1791</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8891</v>
+        <v>-2.3814</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0785</v>
+        <v>-3.2232</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1894</v>
+        <v>0.8417</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8131</v>
@@ -1156,13 +1156,13 @@
         <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2097</v>
+        <v>-0.2827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4693</v>
+        <v>-0.6141</v>
       </c>
       <c r="U9" t="n">
-        <v>0.679</v>
+        <v>0.3314</v>
       </c>
       <c r="V9" t="n">
         <v>0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.717</v>
+        <v>-4.4521</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9617</v>
+        <v>-2.7962</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7552</v>
+        <v>-1.6559</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4316</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8992</v>
+        <v>-0.6343</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.607</v>
+        <v>-0.4415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2922</v>
+        <v>-0.1928</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.3541</v>
+        <v>13.4578</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7797</v>
+        <v>-0.6760000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>14.1337</v>
+        <v>14.1338</v>
       </c>
       <c r="G11" t="n">
         <v>19.3762</v>
@@ -1303,7 +1303,7 @@
         <v>1.6834</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.792400000000001</v>
+        <v>-5.792399999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-23.1694</v>
@@ -1312,19 +1312,19 @@
         <v>17.3769</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5154</v>
+        <v>-0.4118000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.6232</v>
+        <v>-1.5197</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1077</v>
+        <v>1.1078</v>
       </c>
       <c r="V11" t="n">
         <v>0.2856000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>3.5552</v>
+        <v>3.555200000000001</v>
       </c>
       <c r="X11" t="n">
         <v>-3.2696</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.0886</v>
+        <v>1.4172</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5131</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5755</v>
+        <v>1.352</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1067</v>
@@ -1390,13 +1390,13 @@
         <v>2.3169</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5468</v>
+        <v>1.8754</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7024</v>
+        <v>1.2545</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8444</v>
+        <v>0.6209</v>
       </c>
       <c r="V12" t="n">
         <v>0.6138</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GUERRA LOZANO</t>
+          <t>L. BLANCO CENTENO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.099</v>
+        <v>1.033</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4632</v>
+        <v>0.4816</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5622</v>
+        <v>0.5514</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4534</v>
+        <v>0.3089</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.856</v>
+        <v>-1.1311</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4025</v>
+        <v>1.44</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8174</v>
+        <v>0.6541</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9038</v>
+        <v>-0.6481</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9135</v>
+        <v>1.3022</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2708</v>
+        <v>-0.3451</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.7598</v>
+        <v>-0.483</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.511</v>
+        <v>0.1379</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4754</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.4408</v>
+        <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3015</v>
+        <v>0.1448</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9093</v>
+        <v>-0.1725</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3922</v>
+        <v>0.3173</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. BLANCO CENTENO</t>
+          <t>A. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.4247</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3781</v>
+        <v>-1.1871</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5266</v>
+        <v>1.6119</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3089</v>
+        <v>-1.4534</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1311</v>
+        <v>-1.856</v>
       </c>
       <c r="I14" t="n">
-        <v>1.44</v>
+        <v>0.4025</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6541</v>
+        <v>1.8174</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6481</v>
+        <v>0.9038</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3022</v>
+        <v>0.9135</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3451</v>
+        <v>-3.2708</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.483</v>
+        <v>-2.7598</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1379</v>
+        <v>-0.511</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.4754</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5792</v>
+        <v>4.4408</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0166</v>
+        <v>0.6272</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2759</v>
+        <v>0.1853</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2925</v>
+        <v>0.4419</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.916</v>
+        <v>-1.2595</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.773</v>
+        <v>-1.2096</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8569</v>
+        <v>-0.0499</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.0592</v>
+        <v>-1.5284</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.179</v>
+        <v>0.2281</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1198</v>
+        <v>-1.7565</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.865</v>
+        <v>1.6661</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1092</v>
+        <v>2.2289</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2442</v>
+        <v>-0.5628</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1942</v>
+        <v>-3.1945</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0698</v>
+        <v>-2.0008</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1244</v>
+        <v>-1.1937</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3169</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-5.4062</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3169</v>
+        <v>3.8616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1545</v>
+        <v>0.5859</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5797</v>
+        <v>0.0752</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7342</v>
+        <v>0.5107</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3282</v>
+        <v>1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3282</v>
+        <v>2.4554</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2884</v>
+        <v>-1.5739</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.313</v>
+        <v>-2.0832</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0246</v>
+        <v>0.5093</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5284</v>
+        <v>-3.0592</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2281</v>
+        <v>-3.179</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7565</v>
+        <v>0.1198</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6661</v>
+        <v>-0.865</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2289</v>
+        <v>-1.1092</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5628</v>
+        <v>0.2442</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1945</v>
+        <v>-2.1942</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0008</v>
+        <v>-2.0698</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1937</v>
+        <v>-0.1244</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.4062</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8616</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.5034</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0282</v>
+        <v>-0.89</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.3866</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4554</v>
+        <v>-0.3282</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.2157</v>
+        <v>-1.9331</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0887</v>
+        <v>-1.0545</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1269</v>
+        <v>-0.8786</v>
       </c>
       <c r="G17" t="n">
         <v>-3.2482</v>
@@ -1780,13 +1780,13 @@
         <v>3.0892</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6552</v>
+        <v>-0.3727</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2417</v>
+        <v>-0.2074</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4136</v>
+        <v>-0.1652</v>
       </c>
       <c r="V17" t="n">
         <v>-0.243</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.0289</v>
+        <v>-4.6315</v>
       </c>
       <c r="E18" t="n">
         <v>-4.6991</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3297</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-3.779</v>
@@ -1858,13 +1858,13 @@
         <v>2.51</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9216</v>
+        <v>-0.5243</v>
       </c>
       <c r="T18" t="n">
         <v>-0.8004</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1212</v>
+        <v>0.2761</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3282</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.9974</v>
+        <v>-5.8309</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.6879</v>
+        <v>-4.4469</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3095</v>
+        <v>-1.384</v>
       </c>
       <c r="G19" t="n">
         <v>-6.5101</v>
@@ -1936,13 +1936,13 @@
         <v>4.0546</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.484</v>
+        <v>-0.3175</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.7935</v>
+        <v>-0.5524</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3094</v>
+        <v>0.2349</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5133</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.3541</v>
+        <v>-12.354</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.1337</v>
+        <v>-14.1336</v>
       </c>
       <c r="F20" t="n">
-        <v>1.779699999999999</v>
+        <v>1.7797</v>
       </c>
       <c r="G20" t="n">
         <v>-19.3761</v>
@@ -2002,7 +2002,7 @@
         <v>-15.8681</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.5895</v>
+        <v>-4.589499999999999</v>
       </c>
       <c r="P20" t="n">
         <v>5.7923</v>
@@ -2014,19 +2014,19 @@
         <v>23.1692</v>
       </c>
       <c r="S20" t="n">
-        <v>1.515600000000001</v>
+        <v>1.5154</v>
       </c>
       <c r="T20" t="n">
         <v>-1.1077</v>
       </c>
       <c r="U20" t="n">
-        <v>2.6231</v>
+        <v>2.6232</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2856000000000002</v>
+        <v>-0.2856000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2696</v>
+        <v>3.269600000000001</v>
       </c>
       <c r="X20" t="n">
         <v>-3.5552</v>
